--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.008417747105701008</v>
       </c>
       <c r="C2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>14437006</v>
+        <v>4625210</v>
       </c>
       <c r="L2" t="n">
-        <v>8923437</v>
+        <v>2730598</v>
       </c>
       <c r="M2" t="n">
-        <v>2326919</v>
+        <v>685328</v>
       </c>
       <c r="N2" t="n">
-        <v>122109</v>
+        <v>31593</v>
       </c>
       <c r="O2" t="n">
-        <v>1368412</v>
+        <v>414746</v>
       </c>
       <c r="P2" t="n">
-        <v>536505</v>
+        <v>167634</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999330639839172</v>
+        <v>0.9999347329139709</v>
       </c>
       <c r="R2" t="n">
-        <v>0.954042375087738</v>
+        <v>0.9151229858398438</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8951310515403748</v>
+        <v>0.8229536414146423</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8739480376243591</v>
+        <v>0.7749703526496887</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6885043382644653</v>
+        <v>0.5295063853263855</v>
       </c>
       <c r="V2" t="n">
-        <v>0.898043692111969</v>
+        <v>0.8193678855895996</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9192742705345154</v>
+        <v>0.8649934530258179</v>
       </c>
       <c r="X2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="AG2" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AH2" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AI2" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566799402236938</v>
+        <v>0.9565494656562805</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112439155578613</v>
+        <v>0.9113017320632935</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581776022911072</v>
+        <v>0.8579359650611877</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626315712928772</v>
+        <v>0.6623888611793518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020464420318604</v>
+        <v>0.9020065665245056</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002018670822238358</v>
       </c>
       <c r="C3" t="n">
-        <v>594</v>
+        <v>199</v>
       </c>
       <c r="D3" t="n">
-        <v>14437006</v>
+        <v>4625210</v>
       </c>
       <c r="E3" t="n">
-        <v>655238</v>
+        <v>398206</v>
       </c>
       <c r="F3" t="n">
-        <v>7276</v>
+        <v>4151</v>
       </c>
       <c r="G3" t="n">
-        <v>1172</v>
+        <v>660</v>
       </c>
       <c r="H3" t="n">
-        <v>408</v>
+        <v>254</v>
       </c>
       <c r="I3" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="J3" t="n">
-        <v>30048598</v>
+        <v>10016210</v>
       </c>
       <c r="K3" t="n">
-        <v>33191610</v>
+        <v>10871913</v>
       </c>
       <c r="L3" t="n">
-        <v>38164514</v>
+        <v>12477960</v>
       </c>
       <c r="M3" t="n">
-        <v>45857896</v>
+        <v>15198480</v>
       </c>
       <c r="N3" t="n">
-        <v>48666357</v>
+        <v>16212399</v>
       </c>
       <c r="O3" t="n">
-        <v>47306506</v>
+        <v>15728990</v>
       </c>
       <c r="P3" t="n">
-        <v>48361841</v>
+        <v>16110135</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9559831023216248</v>
+        <v>0.9197621941566467</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9125230312347412</v>
+        <v>0.8365310430526733</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8324439525604248</v>
+        <v>0.7352358102798462</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4569981694221497</v>
+        <v>0.3544637560844421</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8961816430091858</v>
+        <v>0.8145403265953064</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9252542853355408</v>
+        <v>0.8672174215316772</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="Z3" t="n">
-        <v>593526</v>
+        <v>197896</v>
       </c>
       <c r="AA3" t="n">
-        <v>25572</v>
+        <v>8540</v>
       </c>
       <c r="AB3" t="n">
-        <v>20336</v>
+        <v>6789</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30049866</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>33232195</v>
+        <v>11082162</v>
       </c>
       <c r="AG3" t="n">
-        <v>38343158</v>
+        <v>12776309</v>
       </c>
       <c r="AH3" t="n">
-        <v>45797268</v>
+        <v>15265103</v>
       </c>
       <c r="AI3" t="n">
-        <v>48631528</v>
+        <v>16210402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47312358</v>
+        <v>15770546</v>
       </c>
       <c r="AK3" t="n">
-        <v>48369192</v>
+        <v>16123045</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576433300971985</v>
+        <v>0.957583487033844</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.910033106803894</v>
+        <v>0.9099507331848145</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577702045440674</v>
+        <v>0.8576524257659912</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.662115752696991</v>
+        <v>0.6619057655334473</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016677737236023</v>
+        <v>0.9016434550285339</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03186393749853683</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>648626</v>
+        <v>403454</v>
       </c>
       <c r="E4" t="n">
-        <v>8923437</v>
+        <v>2730598</v>
       </c>
       <c r="F4" t="n">
-        <v>195819</v>
+        <v>121433</v>
       </c>
       <c r="G4" t="n">
-        <v>3635</v>
+        <v>2593</v>
       </c>
       <c r="H4" t="n">
-        <v>6899</v>
+        <v>5735</v>
       </c>
       <c r="I4" t="n">
-        <v>445</v>
+        <v>379</v>
       </c>
       <c r="J4" t="n">
-        <v>1268</v>
+        <v>412</v>
       </c>
       <c r="K4" t="n">
-        <v>695452</v>
+        <v>428985</v>
       </c>
       <c r="L4" t="n">
-        <v>1045424</v>
+        <v>587448</v>
       </c>
       <c r="M4" t="n">
-        <v>335618</v>
+        <v>199000</v>
       </c>
       <c r="N4" t="n">
-        <v>55245</v>
+        <v>28072</v>
       </c>
       <c r="O4" t="n">
-        <v>155358</v>
+        <v>91432</v>
       </c>
       <c r="P4" t="n">
-        <v>47113</v>
+        <v>26164</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999966561794281</v>
+        <v>0.9999673962593079</v>
       </c>
       <c r="R4" t="n">
-        <v>0.955011785030365</v>
+        <v>0.9174367785453796</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9037433862686157</v>
+        <v>0.8296868205070496</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8526912331581116</v>
+        <v>0.7545803189277649</v>
       </c>
       <c r="U4" t="n">
-        <v>0.549357533454895</v>
+        <v>0.4246542155742645</v>
       </c>
       <c r="V4" t="n">
-        <v>0.897111713886261</v>
+        <v>0.8169469237327576</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9222545623779297</v>
+        <v>0.8661040067672729</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>611398</v>
+        <v>204218</v>
       </c>
       <c r="Z4" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AA4" t="n">
-        <v>248302</v>
+        <v>83015</v>
       </c>
       <c r="AB4" t="n">
-        <v>16438</v>
+        <v>5489</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>654867</v>
+        <v>218736</v>
       </c>
       <c r="AG4" t="n">
-        <v>866780</v>
+        <v>289099</v>
       </c>
       <c r="AH4" t="n">
-        <v>396246</v>
+        <v>132377</v>
       </c>
       <c r="AI4" t="n">
-        <v>90074</v>
+        <v>30069</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149506</v>
+        <v>49876</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571613669395447</v>
+        <v>0.9570662379264832</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106380939483643</v>
+        <v>0.910625696182251</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579738140106201</v>
+        <v>0.8577942252159119</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623735427856445</v>
+        <v>0.6621472835540771</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018570184707642</v>
+        <v>0.9018250107765198</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>172</v>
       </c>
       <c r="D5" t="n">
-        <v>28402</v>
+        <v>15261</v>
       </c>
       <c r="E5" t="n">
-        <v>333037</v>
+        <v>166022</v>
       </c>
       <c r="F5" t="n">
-        <v>2326919</v>
+        <v>685328</v>
       </c>
       <c r="G5" t="n">
-        <v>23403</v>
+        <v>12110</v>
       </c>
       <c r="H5" t="n">
-        <v>79627</v>
+        <v>50686</v>
       </c>
       <c r="I5" t="n">
-        <v>3383</v>
+        <v>2541</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>664732</v>
+        <v>403492</v>
       </c>
       <c r="L5" t="n">
-        <v>855425</v>
+        <v>533594</v>
       </c>
       <c r="M5" t="n">
-        <v>468367</v>
+        <v>246792</v>
       </c>
       <c r="N5" t="n">
-        <v>145089</v>
+        <v>57536</v>
       </c>
       <c r="O5" t="n">
-        <v>158524</v>
+        <v>94432</v>
       </c>
       <c r="P5" t="n">
-        <v>43341</v>
+        <v>25667</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999741315841675</v>
+        <v>0.99997478723526</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9722347855567932</v>
+        <v>0.9490203857421875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9611982703208923</v>
+        <v>0.9313490986824036</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9835883975028992</v>
+        <v>0.9727003574371338</v>
       </c>
       <c r="U5" t="n">
-        <v>0.99591064453125</v>
+        <v>0.9947574734687805</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9935927987098694</v>
+        <v>0.9886179566383362</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9981535673141479</v>
+        <v>0.9968259334564209</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23984</v>
+        <v>8010</v>
       </c>
       <c r="Z5" t="n">
-        <v>254565</v>
+        <v>84966</v>
       </c>
       <c r="AA5" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AB5" t="n">
-        <v>29795</v>
+        <v>9941</v>
       </c>
       <c r="AC5" t="n">
-        <v>87330</v>
+        <v>29135</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>639659</v>
+        <v>213300</v>
       </c>
       <c r="AG5" t="n">
-        <v>879774</v>
+        <v>293938</v>
       </c>
       <c r="AH5" t="n">
-        <v>397573</v>
+        <v>132685</v>
       </c>
       <c r="AI5" t="n">
-        <v>90282</v>
+        <v>30134</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150147</v>
+        <v>50081</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735750555992126</v>
+        <v>0.9735427498817444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643478989601135</v>
+        <v>0.9642956852912903</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837958812713623</v>
+        <v>0.9837679862976074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963183999061584</v>
+        <v>0.9963132739067078</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938832521438599</v>
+        <v>0.9938787817955017</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983758926391602</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>18256</v>
+        <v>10182</v>
       </c>
       <c r="E6" t="n">
-        <v>50511</v>
+        <v>17579</v>
       </c>
       <c r="F6" t="n">
-        <v>46755</v>
+        <v>17840</v>
       </c>
       <c r="G6" t="n">
-        <v>122109</v>
+        <v>31593</v>
       </c>
       <c r="H6" t="n">
-        <v>28009</v>
+        <v>11095</v>
       </c>
       <c r="I6" t="n">
-        <v>1443</v>
+        <v>808</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19318</v>
+        <v>6452</v>
       </c>
       <c r="Z6" t="n">
-        <v>16016</v>
+        <v>5347</v>
       </c>
       <c r="AA6" t="n">
-        <v>32584</v>
+        <v>10875</v>
       </c>
       <c r="AB6" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AC6" t="n">
-        <v>20921</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="E7" t="n">
-        <v>6289</v>
+        <v>5390</v>
       </c>
       <c r="F7" t="n">
-        <v>84180</v>
+        <v>54350</v>
       </c>
       <c r="G7" t="n">
-        <v>26149</v>
+        <v>12220</v>
       </c>
       <c r="H7" t="n">
-        <v>1368412</v>
+        <v>414746</v>
       </c>
       <c r="I7" t="n">
-        <v>41798</v>
+        <v>22414</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2430</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>88798</v>
+        <v>29617</v>
       </c>
       <c r="AB7" t="n">
-        <v>22710</v>
+        <v>7585</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>349</v>
+        <v>251</v>
       </c>
       <c r="F8" t="n">
-        <v>1588</v>
+        <v>1226</v>
       </c>
       <c r="G8" t="n">
-        <v>886</v>
+        <v>489</v>
       </c>
       <c r="H8" t="n">
-        <v>40415</v>
+        <v>23662</v>
       </c>
       <c r="I8" t="n">
-        <v>536505</v>
+        <v>167634</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
